--- a/Team-Data/2008-09/2-19-2008-09.xlsx
+++ b/Team-Data/2008-09/2-19-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
@@ -766,13 +833,13 @@
         <v>8</v>
       </c>
       <c r="AM2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
         <v>13</v>
       </c>
       <c r="AO2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP2" t="n">
         <v>8</v>
@@ -781,7 +848,7 @@
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
         <v>19</v>
@@ -793,7 +860,7 @@
         <v>15</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
         <v>8</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -846,13 +913,13 @@
         <v>55</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>0.782</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -861,7 +928,7 @@
         <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.483</v>
@@ -873,7 +940,7 @@
         <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.386</v>
+        <v>0.384</v>
       </c>
       <c r="O3" t="n">
         <v>20.1</v>
@@ -882,16 +949,16 @@
         <v>25.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="R3" t="n">
         <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
         <v>22.8</v>
@@ -900,25 +967,25 @@
         <v>15.8</v>
       </c>
       <c r="W3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
         <v>23.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.2</v>
+        <v>101.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>4</v>
@@ -927,10 +994,10 @@
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
         <v>11</v>
@@ -960,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
@@ -981,16 +1048,16 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
@@ -1124,13 +1191,13 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN4" t="n">
         <v>18</v>
@@ -1139,7 +1206,7 @@
         <v>24</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
         <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>0.434</v>
+        <v>0.444</v>
       </c>
       <c r="H5" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
@@ -1240,61 +1307,61 @@
         <v>0.376</v>
       </c>
       <c r="O5" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="P5" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.789</v>
+        <v>0.788</v>
       </c>
       <c r="R5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T5" t="n">
         <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V5" t="n">
         <v>15.1</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
         <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.4</v>
+        <v>100.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.9</v>
+        <v>-1.6</v>
       </c>
       <c r="AD5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF5" t="n">
         <v>17</v>
       </c>
-      <c r="AE5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>18</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>19</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
@@ -1306,22 +1373,22 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
         <v>22</v>
       </c>
       <c r="AM5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN5" t="n">
         <v>9</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1330,7 +1397,7 @@
         <v>8</v>
       </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
         <v>11</v>
@@ -1351,10 +1418,10 @@
         <v>28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -1389,49 +1456,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
         <v>41</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.804</v>
+        <v>0.788</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="n">
-        <v>78.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.383</v>
+        <v>0.38</v>
       </c>
       <c r="O6" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P6" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q6" t="n">
         <v>0.752</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S6" t="n">
         <v>31.2</v>
@@ -1440,43 +1507,43 @@
         <v>41.9</v>
       </c>
       <c r="U6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>101</v>
+        <v>100.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
@@ -1491,25 +1558,25 @@
         <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
         <v>22</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1521,7 +1588,7 @@
         <v>24</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
         <v>9</v>
@@ -1530,10 +1597,10 @@
         <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA6" t="n">
         <v>23</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1703,7 +1770,7 @@
         <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>14</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1846,7 +1913,7 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ8" t="n">
         <v>25</v>
@@ -1906,7 +1973,7 @@
         <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -1935,61 +2002,61 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>0.509</v>
+        <v>0.519</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J9" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M9" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.346</v>
+        <v>0.349</v>
       </c>
       <c r="O9" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P9" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="R9" t="n">
         <v>10.8</v>
       </c>
       <c r="S9" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T9" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="U9" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V9" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="W9" t="n">
         <v>6.4</v>
@@ -2001,31 +2068,31 @@
         <v>4</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.5</v>
+        <v>93.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
         <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI9" t="n">
         <v>21</v>
@@ -2034,7 +2101,7 @@
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL9" t="n">
         <v>27</v>
@@ -2043,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="AN9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP9" t="n">
         <v>25</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>26</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
@@ -2058,7 +2125,7 @@
         <v>18</v>
       </c>
       <c r="AS9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT9" t="n">
         <v>19</v>
@@ -2073,10 +2140,10 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2283,7 @@
         <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2389,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>27</v>
@@ -2413,7 +2480,7 @@
         <v>10</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2589,10 +2656,10 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP12" t="n">
         <v>21</v>
@@ -2628,7 +2695,7 @@
         <v>30</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO13" t="n">
         <v>27</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="J14" t="n">
-        <v>85.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="K14" t="n">
         <v>0.478</v>
@@ -2872,34 +2939,34 @@
         <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="O14" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="P14" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R14" t="n">
         <v>12.8</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T14" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V14" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W14" t="n">
         <v>8.300000000000001</v>
@@ -2911,19 +2978,19 @@
         <v>4.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>109</v>
+        <v>108.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2935,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2944,16 +3011,16 @@
         <v>4</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2968,7 +3035,7 @@
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2989,10 +3056,10 @@
         <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3171,7 +3238,7 @@
         <v>21</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3320,7 +3387,7 @@
         <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP16" t="n">
         <v>23</v>
@@ -3350,7 +3417,7 @@
         <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AZ16" t="n">
         <v>12</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" t="n">
         <v>27</v>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
-        <v>0.482</v>
+        <v>0.474</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3409,10 +3476,10 @@
         <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L17" t="n">
         <v>5.8</v>
@@ -3421,13 +3488,13 @@
         <v>16.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="P17" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q17" t="n">
         <v>0.783</v>
@@ -3436,10 +3503,10 @@
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="U17" t="n">
         <v>21.5</v>
@@ -3448,25 +3515,25 @@
         <v>14.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X17" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y17" t="n">
         <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3487,7 +3554,7 @@
         <v>15</v>
       </c>
       <c r="AJ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK17" t="n">
         <v>21</v>
@@ -3502,7 +3569,7 @@
         <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP17" t="n">
         <v>7</v>
@@ -3523,7 +3590,7 @@
         <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>16</v>
@@ -3532,7 +3599,7 @@
         <v>28</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3684,7 +3751,7 @@
         <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP18" t="n">
         <v>14</v>
@@ -3705,7 +3772,7 @@
         <v>21</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW18" t="n">
         <v>26</v>
@@ -3720,10 +3787,10 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3909,7 @@
         <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
@@ -3860,19 +3927,19 @@
         <v>7</v>
       </c>
       <c r="AM19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN19" t="n">
         <v>8</v>
       </c>
       <c r="AO19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR19" t="n">
         <v>14</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
       </c>
       <c r="AF20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG20" t="n">
         <v>8</v>
@@ -4036,7 +4103,7 @@
         <v>30</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>9</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
@@ -4263,7 +4330,7 @@
         <v>24</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>7.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4627,7 +4694,7 @@
         <v>3</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>0.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH24" t="n">
         <v>27</v>
@@ -4788,7 +4855,7 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
         <v>7</v>
@@ -4809,7 +4876,7 @@
         <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>13</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4955,7 +5022,7 @@
         <v>20</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>4</v>
@@ -4985,10 +5052,10 @@
         <v>27</v>
       </c>
       <c r="AX25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
         <v>11</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -5029,55 +5096,55 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E26" t="n">
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.635</v>
+        <v>0.623</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N26" t="n">
         <v>0.383</v>
       </c>
       <c r="O26" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.764</v>
+        <v>0.762</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T26" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U26" t="n">
         <v>20.4</v>
@@ -5095,19 +5162,19 @@
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA26" t="n">
         <v>21.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.2</v>
+        <v>98.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5119,34 +5186,34 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
         <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
       </c>
       <c r="AM26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>19</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>18</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5176,13 +5243,13 @@
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5389,7 @@
         <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP27" t="n">
         <v>13</v>
@@ -5361,7 +5428,7 @@
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -5393,64 +5460,64 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E28" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F28" t="n">
         <v>17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.679</v>
+        <v>0.673</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
       </c>
       <c r="I28" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J28" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L28" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.392</v>
+        <v>0.391</v>
       </c>
       <c r="O28" t="n">
         <v>15.8</v>
       </c>
       <c r="P28" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T28" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U28" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V28" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="W28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="X28" t="n">
         <v>4.2</v>
@@ -5459,19 +5526,19 @@
         <v>4.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA28" t="n">
         <v>18.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.7</v>
+        <v>98</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5486,19 +5553,19 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ28" t="n">
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN28" t="n">
         <v>2</v>
@@ -5510,13 +5577,13 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
         <v>20</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5686,10 +5753,10 @@
         <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,7 +5765,7 @@
         <v>30</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
@@ -5713,7 +5780,7 @@
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5722,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -5757,58 +5824,58 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F30" t="n">
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>0.582</v>
+        <v>0.574</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J30" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K30" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="M30" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.338</v>
+        <v>0.34</v>
       </c>
       <c r="O30" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="P30" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R30" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S30" t="n">
         <v>29.2</v>
       </c>
       <c r="T30" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U30" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="V30" t="n">
         <v>15.1</v>
@@ -5826,19 +5893,19 @@
         <v>22.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>102.6</v>
+        <v>102.8</v>
       </c>
       <c r="AC30" t="n">
         <v>2.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE30" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AF30" t="n">
         <v>12</v>
@@ -5847,7 +5914,7 @@
         <v>12</v>
       </c>
       <c r="AH30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI30" t="n">
         <v>7</v>
@@ -5856,7 +5923,7 @@
         <v>18</v>
       </c>
       <c r="AK30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5874,10 +5941,10 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
         <v>22</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6035,7 +6102,7 @@
         <v>19</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
         <v>25</v>
@@ -6056,10 +6123,10 @@
         <v>28</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-19-2008-09</t>
+          <t>2009-02-19</t>
         </is>
       </c>
     </row>
